--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="R40b3e681df024f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="R0ee372acb99e415e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -159,95 +159,98 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="31">
+  <x:cellXfs count="32">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -470,144 +473,144 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="24" t="str">
+      <x:c r="A1" s="25" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="9" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="9" t="str">
+      <x:c r="C1" s="10" t="str">
         <x:v>parent</x:v>
       </x:c>
-      <x:c r="D1" s="9" t="str">
+      <x:c r="D1" s="10" t="str">
         <x:v>valueType</x:v>
       </x:c>
-      <x:c r="E1" s="9" t="str">
+      <x:c r="E1" s="10" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="F1" s="9" t="str">
+      <x:c r="F1" s="10" t="str">
         <x:v>sep</x:v>
       </x:c>
-      <x:c r="G1" s="9" t="str">
+      <x:c r="G1" s="10" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="H1" s="9" t="str">
+      <x:c r="H1" s="10" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="I1" s="9" t="str">
+      <x:c r="I1" s="10" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="J1" s="9" t="str">
+      <x:c r="J1" s="10" t="str">
         <x:v>*fields</x:v>
       </x:c>
-      <x:c r="K1" s="9"/>
-      <x:c r="L1" s="9"/>
-      <x:c r="M1" s="9"/>
-      <x:c r="N1" s="9"/>
-      <x:c r="O1" s="9"/>
-      <x:c r="P1" s="10"/>
+      <x:c r="K1" s="10"/>
+      <x:c r="L1" s="10"/>
+      <x:c r="M1" s="10"/>
+      <x:c r="N1" s="10"/>
+      <x:c r="O1" s="10"/>
+      <x:c r="P1" s="11"/>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="28" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B2" s="13"/>
-      <x:c r="C2" s="13"/>
-      <x:c r="D2" s="13"/>
-      <x:c r="E2" s="13"/>
-      <x:c r="F2" s="13"/>
-      <x:c r="G2" s="13"/>
-      <x:c r="H2" s="13"/>
-      <x:c r="I2" s="13"/>
-      <x:c r="J2" s="13" t="str">
+      <x:c r="B2" s="14"/>
+      <x:c r="C2" s="14"/>
+      <x:c r="D2" s="14"/>
+      <x:c r="E2" s="14"/>
+      <x:c r="F2" s="14"/>
+      <x:c r="G2" s="14"/>
+      <x:c r="H2" s="14"/>
+      <x:c r="I2" s="14"/>
+      <x:c r="J2" s="14" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="K2" s="13" t="str">
+      <x:c r="K2" s="14" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="L2" s="13" t="str">
+      <x:c r="L2" s="14" t="str">
         <x:v>type</x:v>
       </x:c>
-      <x:c r="M2" s="13" t="str">
+      <x:c r="M2" s="14" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="N2" s="13" t="str">
+      <x:c r="N2" s="14" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="O2" s="13" t="str">
+      <x:c r="O2" s="14" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="P2" s="13" t="str">
+      <x:c r="P2" s="14" t="str">
         <x:v>variants</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="29" t="str">
+      <x:c r="A3" s="30" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
+      <x:c r="B3" s="16" t="str">
         <x:v>完整类型名</x:v>
       </x:c>
-      <x:c r="C3" s="15" t="str">
+      <x:c r="C3" s="16" t="str">
         <x:v>父类型</x:v>
       </x:c>
-      <x:c r="D3" s="15" t="str">
+      <x:c r="D3" s="16" t="str">
         <x:v>值类型</x:v>
       </x:c>
-      <x:c r="E3" s="15" t="str">
+      <x:c r="E3" s="16" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="F3" s="15" t="str">
+      <x:c r="F3" s="16" t="str">
         <x:v>分隔符</x:v>
       </x:c>
-      <x:c r="G3" s="15" t="str">
+      <x:c r="G3" s="16" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="H3" s="15" t="str">
+      <x:c r="H3" s="16" t="str">
         <x:v>标签</x:v>
       </x:c>
-      <x:c r="I3" s="15" t="str">
+      <x:c r="I3" s="16" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="J3" s="15" t="str">
+      <x:c r="J3" s="16" t="str">
         <x:v>字段名</x:v>
       </x:c>
-      <x:c r="K3" s="15" t="str">
+      <x:c r="K3" s="16" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="L3" s="15" t="str">
+      <x:c r="L3" s="16" t="str">
         <x:v>字段类型</x:v>
       </x:c>
-      <x:c r="M3" s="15" t="str">
+      <x:c r="M3" s="16" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="N3" s="15" t="str">
+      <x:c r="N3" s="16" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="O3" s="15" t="str">
+      <x:c r="O3" s="16" t="str">
         <x:v>标签</x:v>
       </x:c>
-      <x:c r="P3" s="15" t="str">
+      <x:c r="P3" s="16" t="str">
         <x:v>变体</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="30"/>
-      <x:c r="B4" s="22"/>
-      <x:c r="C4" s="22"/>
-      <x:c r="D4" s="22"/>
-      <x:c r="E4" s="22"/>
-      <x:c r="F4" s="22"/>
-      <x:c r="G4" s="22"/>
-      <x:c r="H4" s="22"/>
-      <x:c r="I4" s="22"/>
-      <x:c r="J4" s="22"/>
-      <x:c r="K4" s="22"/>
-      <x:c r="L4" s="22"/>
-      <x:c r="M4" s="22"/>
-      <x:c r="N4" s="22"/>
-      <x:c r="O4" s="22"/>
-      <x:c r="P4" s="23"/>
+      <x:c r="A4" s="31"/>
+      <x:c r="B4" s="23"/>
+      <x:c r="C4" s="23"/>
+      <x:c r="D4" s="23"/>
+      <x:c r="E4" s="23"/>
+      <x:c r="F4" s="23"/>
+      <x:c r="G4" s="23"/>
+      <x:c r="H4" s="23"/>
+      <x:c r="I4" s="23"/>
+      <x:c r="J4" s="23"/>
+      <x:c r="K4" s="23"/>
+      <x:c r="L4" s="23"/>
+      <x:c r="M4" s="23"/>
+      <x:c r="N4" s="23"/>
+      <x:c r="O4" s="23"/>
+      <x:c r="P4" s="24"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="R0ee372acb99e415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="Rca9bf11bc5de4f17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -159,7 +159,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -251,12 +251,43 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -594,23 +625,67 @@
         <x:v>变体</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="30" customHeight="1">
+    <x:row r="4" ht="28" customHeight="1">
       <x:c r="A4" s="31"/>
-      <x:c r="B4" s="23"/>
+      <x:c r="B4" s="23" t="str">
+        <x:v>AttributeValue</x:v>
+      </x:c>
       <x:c r="C4" s="23"/>
-      <x:c r="D4" s="23"/>
+      <x:c r="D4" s="32" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E4" s="23"/>
-      <x:c r="F4" s="23"/>
-      <x:c r="G4" s="23"/>
+      <x:c r="F4" s="23" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G4" s="23" t="str">
+        <x:v>属性值；由属性方案显式配置</x:v>
+      </x:c>
       <x:c r="H4" s="23"/>
-      <x:c r="I4" s="23"/>
-      <x:c r="J4" s="23"/>
+      <x:c r="I4" s="23" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J4" s="23" t="str">
+        <x:v>attributeId</x:v>
+      </x:c>
       <x:c r="K4" s="23"/>
-      <x:c r="L4" s="23"/>
-      <x:c r="M4" s="23"/>
-      <x:c r="N4" s="23"/>
+      <x:c r="L4" s="23" t="str">
+        <x:v>int#ref=TbAttribute</x:v>
+      </x:c>
+      <x:c r="M4" s="23" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N4" s="23" t="str">
+        <x:v>属性ID</x:v>
+      </x:c>
       <x:c r="O4" s="23"/>
       <x:c r="P4" s="24"/>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="34"/>
+      <x:c r="B5" s="34"/>
+      <x:c r="C5" s="34"/>
+      <x:c r="D5" s="34"/>
+      <x:c r="E5" s="34"/>
+      <x:c r="F5" s="34"/>
+      <x:c r="G5" s="34"/>
+      <x:c r="H5" s="34"/>
+      <x:c r="I5" s="34"/>
+      <x:c r="J5" s="34" t="str">
+        <x:v>value</x:v>
+      </x:c>
+      <x:c r="K5" s="34"/>
+      <x:c r="L5" s="34" t="str">
+        <x:v>double</x:v>
+      </x:c>
+      <x:c r="M5" s="34" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N5" s="34" t="str">
+        <x:v>属性基础值</x:v>
+      </x:c>
+      <x:c r="O5" s="34"/>
+      <x:c r="P5" s="34"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -482,215 +482,221 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="20" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="25" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B1" s="10" t="str">
-        <x:v>full_name</x:v>
-      </x:c>
-      <x:c r="C1" s="10" t="str">
-        <x:v>parent</x:v>
-      </x:c>
-      <x:c r="D1" s="10" t="str">
-        <x:v>valueType</x:v>
-      </x:c>
-      <x:c r="E1" s="10" t="str">
-        <x:v>alias</x:v>
-      </x:c>
-      <x:c r="F1" s="10" t="str">
-        <x:v>sep</x:v>
-      </x:c>
-      <x:c r="G1" s="10" t="str">
-        <x:v>comment</x:v>
-      </x:c>
-      <x:c r="H1" s="10" t="str">
-        <x:v>tags</x:v>
-      </x:c>
-      <x:c r="I1" s="10" t="str">
-        <x:v>group</x:v>
-      </x:c>
-      <x:c r="J1" s="10" t="str">
-        <x:v>*fields</x:v>
-      </x:c>
-      <x:c r="K1" s="10"/>
-      <x:c r="L1" s="10"/>
-      <x:c r="M1" s="10"/>
-      <x:c r="N1" s="10"/>
-      <x:c r="O1" s="10"/>
-      <x:c r="P1" s="11"/>
-    </x:row>
-    <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="29" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B2" s="14"/>
-      <x:c r="C2" s="14"/>
-      <x:c r="D2" s="14"/>
-      <x:c r="E2" s="14"/>
-      <x:c r="F2" s="14"/>
-      <x:c r="G2" s="14"/>
-      <x:c r="H2" s="14"/>
-      <x:c r="I2" s="14"/>
-      <x:c r="J2" s="14" t="str">
-        <x:v>name</x:v>
-      </x:c>
-      <x:c r="K2" s="14" t="str">
-        <x:v>alias</x:v>
-      </x:c>
-      <x:c r="L2" s="14" t="str">
-        <x:v>type</x:v>
-      </x:c>
-      <x:c r="M2" s="14" t="str">
-        <x:v>group</x:v>
-      </x:c>
-      <x:c r="N2" s="14" t="str">
-        <x:v>comment</x:v>
-      </x:c>
-      <x:c r="O2" s="14" t="str">
-        <x:v>tags</x:v>
-      </x:c>
-      <x:c r="P2" s="14" t="str">
-        <x:v>variants</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="30" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B3" s="16" t="str">
-        <x:v>完整类型名</x:v>
-      </x:c>
-      <x:c r="C3" s="16" t="str">
-        <x:v>父类型</x:v>
-      </x:c>
-      <x:c r="D3" s="16" t="str">
-        <x:v>值类型</x:v>
-      </x:c>
-      <x:c r="E3" s="16" t="str">
-        <x:v>别名</x:v>
-      </x:c>
-      <x:c r="F3" s="16" t="str">
-        <x:v>分隔符</x:v>
-      </x:c>
-      <x:c r="G3" s="16" t="str">
-        <x:v>说明</x:v>
-      </x:c>
-      <x:c r="H3" s="16" t="str">
-        <x:v>标签</x:v>
-      </x:c>
-      <x:c r="I3" s="16" t="str">
-        <x:v>分组</x:v>
-      </x:c>
-      <x:c r="J3" s="16" t="str">
-        <x:v>字段名</x:v>
-      </x:c>
-      <x:c r="K3" s="16" t="str">
-        <x:v>别名</x:v>
-      </x:c>
-      <x:c r="L3" s="16" t="str">
-        <x:v>字段类型</x:v>
-      </x:c>
-      <x:c r="M3" s="16" t="str">
-        <x:v>分组</x:v>
-      </x:c>
-      <x:c r="N3" s="16" t="str">
-        <x:v>说明</x:v>
-      </x:c>
-      <x:c r="O3" s="16" t="str">
-        <x:v>标签</x:v>
-      </x:c>
-      <x:c r="P3" s="16" t="str">
-        <x:v>变体</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="28" customHeight="1">
-      <x:c r="A4" s="31"/>
-      <x:c r="B4" s="23" t="str">
-        <x:v>AttributeValue</x:v>
-      </x:c>
-      <x:c r="C4" s="23"/>
-      <x:c r="D4" s="32" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E4" s="23"/>
-      <x:c r="F4" s="23" t="str">
-        <x:v>:</x:v>
-      </x:c>
-      <x:c r="G4" s="23" t="str">
-        <x:v>属性值；由属性方案显式配置</x:v>
-      </x:c>
-      <x:c r="H4" s="23"/>
-      <x:c r="I4" s="23" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="J4" s="23" t="str">
-        <x:v>attributeId</x:v>
-      </x:c>
-      <x:c r="K4" s="23"/>
-      <x:c r="L4" s="23" t="str">
-        <x:v>int#ref=TbAttribute</x:v>
-      </x:c>
-      <x:c r="M4" s="23" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N4" s="23" t="str">
-        <x:v>属性ID</x:v>
-      </x:c>
-      <x:c r="O4" s="23"/>
-      <x:c r="P4" s="24"/>
-    </x:row>
-    <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="34"/>
-      <x:c r="B5" s="34"/>
-      <x:c r="C5" s="34"/>
-      <x:c r="D5" s="34"/>
-      <x:c r="E5" s="34"/>
-      <x:c r="F5" s="34"/>
-      <x:c r="G5" s="34"/>
-      <x:c r="H5" s="34"/>
-      <x:c r="I5" s="34"/>
-      <x:c r="J5" s="34" t="str">
-        <x:v>value</x:v>
-      </x:c>
-      <x:c r="K5" s="34"/>
-      <x:c r="L5" s="34" t="str">
-        <x:v>double</x:v>
-      </x:c>
-      <x:c r="M5" s="34" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="N5" s="34" t="str">
-        <x:v>属性基础值</x:v>
-      </x:c>
-      <x:c r="O5" s="34"/>
-      <x:c r="P5" s="34"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="J1:P1"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="20" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="12" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="25" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B1" s="10" t="str">
+        <v>full_name</v>
+      </c>
+      <c r="C1" s="10" t="str">
+        <v>parent</v>
+      </c>
+      <c r="D1" s="10" t="str">
+        <v>valueType</v>
+      </c>
+      <c r="E1" s="10" t="str">
+        <v>alias</v>
+      </c>
+      <c r="F1" s="10" t="str">
+        <v>sep</v>
+      </c>
+      <c r="G1" s="10" t="str">
+        <v>comment</v>
+      </c>
+      <c r="H1" s="10" t="str">
+        <v>tags</v>
+      </c>
+      <c r="I1" s="10" t="str">
+        <v>group</v>
+      </c>
+      <c r="J1" s="10" t="str">
+        <v>*fields</v>
+      </c>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="11"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="29" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14" t="str">
+        <v>name</v>
+      </c>
+      <c r="K2" s="14" t="str">
+        <v>alias</v>
+      </c>
+      <c r="L2" s="14" t="str">
+        <v>type</v>
+      </c>
+      <c r="M2" s="14" t="str">
+        <v>group</v>
+      </c>
+      <c r="N2" s="14" t="str">
+        <v>comment</v>
+      </c>
+      <c r="O2" s="14" t="str">
+        <v>tags</v>
+      </c>
+      <c r="P2" s="14" t="str">
+        <v>variants</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="30" t="str">
+        <v>##</v>
+      </c>
+      <c r="B3" s="16" t="str">
+        <v>完整类型名</v>
+      </c>
+      <c r="C3" s="16" t="str">
+        <v>父类型</v>
+      </c>
+      <c r="D3" s="16" t="str">
+        <v>值类型</v>
+      </c>
+      <c r="E3" s="16" t="str">
+        <v>别名</v>
+      </c>
+      <c r="F3" s="16" t="str">
+        <v>分隔符</v>
+      </c>
+      <c r="G3" s="16" t="str">
+        <v>说明</v>
+      </c>
+      <c r="H3" s="16" t="str">
+        <v>标签</v>
+      </c>
+      <c r="I3" s="16" t="str">
+        <v>分组</v>
+      </c>
+      <c r="J3" s="16" t="str">
+        <v>字段名</v>
+      </c>
+      <c r="K3" s="16" t="str">
+        <v>别名</v>
+      </c>
+      <c r="L3" s="16" t="str">
+        <v>字段类型</v>
+      </c>
+      <c r="M3" s="16" t="str">
+        <v>分组</v>
+      </c>
+      <c r="N3" s="16" t="str">
+        <v>说明</v>
+      </c>
+      <c r="O3" s="16" t="str">
+        <v>标签</v>
+      </c>
+      <c r="P3" s="16" t="str">
+        <v>变体</v>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="31"/>
+      <c r="B4" s="23" t="str">
+        <v>AttributeValue</v>
+      </c>
+      <c r="C4" s="23"/>
+      <c r="D4" s="32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23" t="str">
+        <v>:</v>
+      </c>
+      <c r="G4" s="23" t="str">
+        <v>属性值；由属性方案显式配置</v>
+      </c>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23" t="str">
+        <v>c</v>
+      </c>
+      <c r="J4" s="23" t="str">
+        <v>attributeId</v>
+      </c>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23" t="str">
+        <v>int#ref=TbAttribute</v>
+      </c>
+      <c r="M4" s="23" t="str">
+        <v>c</v>
+      </c>
+      <c r="N4" s="23" t="str">
+        <v>属性ID</v>
+      </c>
+      <c r="O4" s="23"/>
+      <c r="P4" s="24"/>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="34"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34" t="inlineStr">
+        <is>
+          <t>valueMilli</t>
+        </is>
+      </c>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="M5" s="34" t="str">
+        <v>c</v>
+      </c>
+      <c r="N5" s="34" t="inlineStr">
+        <is>
+          <t>属性基础值；原单位×1000；实际值=表值/1000；最多3位小数</t>
+        </is>
+      </c>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="J1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Config/Datas/__beans__.xlsx
+++ b/Config/Datas/__beans__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="Rca9bf11bc5de4f17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beans" sheetId="1" r:id="Re95b8bb99a30444a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,8 +59,68 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF243B53"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF52606D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF334E68"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -92,8 +152,28 @@
         <x:fgColor rgb="FF64748B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEEF5FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F8FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="7">
+  <x:borders count="8">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -155,11 +235,25 @@
         <x:color rgb="FFCBD5E1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7E0E8"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="80">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -265,6 +359,187 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -482,221 +757,365 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="12" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="20" hidden="0" customWidth="1"/>
-    <col min="13" max="13" width="12" hidden="0" customWidth="1"/>
-    <col min="14" max="14" width="28" hidden="0" customWidth="1"/>
-    <col min="15" max="15" width="14" hidden="0" customWidth="1"/>
-    <col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="25" t="str">
-        <v>##var</v>
-      </c>
-      <c r="B1" s="10" t="str">
-        <v>full_name</v>
-      </c>
-      <c r="C1" s="10" t="str">
-        <v>parent</v>
-      </c>
-      <c r="D1" s="10" t="str">
-        <v>valueType</v>
-      </c>
-      <c r="E1" s="10" t="str">
-        <v>alias</v>
-      </c>
-      <c r="F1" s="10" t="str">
-        <v>sep</v>
-      </c>
-      <c r="G1" s="10" t="str">
-        <v>comment</v>
-      </c>
-      <c r="H1" s="10" t="str">
-        <v>tags</v>
-      </c>
-      <c r="I1" s="10" t="str">
-        <v>group</v>
-      </c>
-      <c r="J1" s="10" t="str">
-        <v>*fields</v>
-      </c>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="11"/>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="29" t="str">
-        <v>##var</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14" t="str">
-        <v>name</v>
-      </c>
-      <c r="K2" s="14" t="str">
-        <v>alias</v>
-      </c>
-      <c r="L2" s="14" t="str">
-        <v>type</v>
-      </c>
-      <c r="M2" s="14" t="str">
-        <v>group</v>
-      </c>
-      <c r="N2" s="14" t="str">
-        <v>comment</v>
-      </c>
-      <c r="O2" s="14" t="str">
-        <v>tags</v>
-      </c>
-      <c r="P2" s="14" t="str">
-        <v>variants</v>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="30" t="str">
-        <v>##</v>
-      </c>
-      <c r="B3" s="16" t="str">
-        <v>完整类型名</v>
-      </c>
-      <c r="C3" s="16" t="str">
-        <v>父类型</v>
-      </c>
-      <c r="D3" s="16" t="str">
-        <v>值类型</v>
-      </c>
-      <c r="E3" s="16" t="str">
-        <v>别名</v>
-      </c>
-      <c r="F3" s="16" t="str">
-        <v>分隔符</v>
-      </c>
-      <c r="G3" s="16" t="str">
-        <v>说明</v>
-      </c>
-      <c r="H3" s="16" t="str">
-        <v>标签</v>
-      </c>
-      <c r="I3" s="16" t="str">
-        <v>分组</v>
-      </c>
-      <c r="J3" s="16" t="str">
-        <v>字段名</v>
-      </c>
-      <c r="K3" s="16" t="str">
-        <v>别名</v>
-      </c>
-      <c r="L3" s="16" t="str">
-        <v>字段类型</v>
-      </c>
-      <c r="M3" s="16" t="str">
-        <v>分组</v>
-      </c>
-      <c r="N3" s="16" t="str">
-        <v>说明</v>
-      </c>
-      <c r="O3" s="16" t="str">
-        <v>标签</v>
-      </c>
-      <c r="P3" s="16" t="str">
-        <v>变体</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="31"/>
-      <c r="B4" s="23" t="str">
-        <v>AttributeValue</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="32" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23" t="str">
-        <v>:</v>
-      </c>
-      <c r="G4" s="23" t="str">
-        <v>属性值；由属性方案显式配置</v>
-      </c>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23" t="str">
-        <v>c</v>
-      </c>
-      <c r="J4" s="23" t="str">
-        <v>attributeId</v>
-      </c>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23" t="str">
-        <v>int#ref=TbAttribute</v>
-      </c>
-      <c r="M4" s="23" t="str">
-        <v>c</v>
-      </c>
-      <c r="N4" s="23" t="str">
-        <v>属性ID</v>
-      </c>
-      <c r="O4" s="23"/>
-      <c r="P4" s="24"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34" t="inlineStr">
-        <is>
-          <t>valueMilli</t>
-        </is>
-      </c>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="M5" s="34" t="str">
-        <v>c</v>
-      </c>
-      <c r="N5" s="34" t="inlineStr">
-        <is>
-          <t>属性基础值；原单位×1000；实际值=表值/1000；最多3位小数</t>
-        </is>
-      </c>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-    </row>
-  </sheetData>
-  <mergeCells>
-    <mergeCell ref="J1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="8" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="8" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="27" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="8" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="8" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="57" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" s="57" t="str">
+        <x:v>full_name</x:v>
+      </x:c>
+      <x:c r="C1" s="57" t="str">
+        <x:v>parent</x:v>
+      </x:c>
+      <x:c r="D1" s="57" t="str">
+        <x:v>valueType</x:v>
+      </x:c>
+      <x:c r="E1" s="57" t="str">
+        <x:v>alias</x:v>
+      </x:c>
+      <x:c r="F1" s="57" t="str">
+        <x:v>sep</x:v>
+      </x:c>
+      <x:c r="G1" s="57" t="str">
+        <x:v>comment</x:v>
+      </x:c>
+      <x:c r="H1" s="57" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="I1" s="57" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="J1" s="57" t="str">
+        <x:v>*fields</x:v>
+      </x:c>
+      <x:c r="K1" s="57"/>
+      <x:c r="L1" s="57"/>
+      <x:c r="M1" s="57"/>
+      <x:c r="N1" s="57"/>
+      <x:c r="O1" s="57"/>
+      <x:c r="P1" s="57"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="59" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B2" s="59"/>
+      <x:c r="C2" s="59"/>
+      <x:c r="D2" s="59"/>
+      <x:c r="E2" s="59"/>
+      <x:c r="F2" s="59"/>
+      <x:c r="G2" s="59"/>
+      <x:c r="H2" s="59"/>
+      <x:c r="I2" s="59"/>
+      <x:c r="J2" s="59" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="K2" s="59" t="str">
+        <x:v>alias</x:v>
+      </x:c>
+      <x:c r="L2" s="59" t="str">
+        <x:v>type</x:v>
+      </x:c>
+      <x:c r="M2" s="59" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="N2" s="59" t="str">
+        <x:v>comment</x:v>
+      </x:c>
+      <x:c r="O2" s="59" t="str">
+        <x:v>tags</x:v>
+      </x:c>
+      <x:c r="P2" s="59" t="str">
+        <x:v>variants</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="62" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B3" s="63" t="str">
+        <x:v>完整类型名</x:v>
+      </x:c>
+      <x:c r="C3" s="63" t="str">
+        <x:v>父类型</x:v>
+      </x:c>
+      <x:c r="D3" s="63" t="str">
+        <x:v>值类型</x:v>
+      </x:c>
+      <x:c r="E3" s="63" t="str">
+        <x:v>别名</x:v>
+      </x:c>
+      <x:c r="F3" s="63" t="str">
+        <x:v>分隔符</x:v>
+      </x:c>
+      <x:c r="G3" s="63" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+      <x:c r="H3" s="63" t="str">
+        <x:v>标签</x:v>
+      </x:c>
+      <x:c r="I3" s="63" t="str">
+        <x:v>分组</x:v>
+      </x:c>
+      <x:c r="J3" s="63" t="str">
+        <x:v>字段名</x:v>
+      </x:c>
+      <x:c r="K3" s="63" t="str">
+        <x:v>别名</x:v>
+      </x:c>
+      <x:c r="L3" s="63" t="str">
+        <x:v>字段类型</x:v>
+      </x:c>
+      <x:c r="M3" s="63" t="str">
+        <x:v>分组</x:v>
+      </x:c>
+      <x:c r="N3" s="63" t="str">
+        <x:v>说明</x:v>
+      </x:c>
+      <x:c r="O3" s="63" t="str">
+        <x:v>标签</x:v>
+      </x:c>
+      <x:c r="P3" s="63" t="str">
+        <x:v>变体</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="67"/>
+      <x:c r="B4" s="68" t="str">
+        <x:v>AttributeValue</x:v>
+      </x:c>
+      <x:c r="C4" s="68"/>
+      <x:c r="D4" s="69" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="68"/>
+      <x:c r="F4" s="68" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G4" s="68" t="str">
+        <x:v>属性值；由属性方案显式配置</x:v>
+      </x:c>
+      <x:c r="H4" s="68"/>
+      <x:c r="I4" s="68" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J4" s="68" t="str">
+        <x:v>attributeId</x:v>
+      </x:c>
+      <x:c r="K4" s="68"/>
+      <x:c r="L4" s="68" t="str">
+        <x:v>int#ref=TbAttribute</x:v>
+      </x:c>
+      <x:c r="M4" s="68" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N4" s="68" t="str">
+        <x:v>属性ID</x:v>
+      </x:c>
+      <x:c r="O4" s="68"/>
+      <x:c r="P4" s="68"/>
+    </x:row>
+    <x:row r="5" ht="28" customHeight="1">
+      <x:c r="A5" s="78"/>
+      <x:c r="B5" s="78"/>
+      <x:c r="C5" s="78"/>
+      <x:c r="D5" s="78"/>
+      <x:c r="E5" s="78"/>
+      <x:c r="F5" s="78"/>
+      <x:c r="G5" s="78"/>
+      <x:c r="H5" s="78"/>
+      <x:c r="I5" s="78"/>
+      <x:c r="J5" s="78" t="str">
+        <x:v>valueMilli</x:v>
+      </x:c>
+      <x:c r="K5" s="78"/>
+      <x:c r="L5" s="78" t="str">
+        <x:v>long</x:v>
+      </x:c>
+      <x:c r="M5" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N5" s="78" t="str">
+        <x:v>属性基础值；原单位×1000；实际值=表值/1000；最多3位小数</x:v>
+      </x:c>
+      <x:c r="O5" s="78"/>
+      <x:c r="P5" s="78"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="78"/>
+      <x:c r="B6" s="78" t="str">
+        <x:v>MonsterWeight</x:v>
+      </x:c>
+      <x:c r="C6" s="78"/>
+      <x:c r="D6" s="79" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="78"/>
+      <x:c r="F6" s="78" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G6" s="78" t="str">
+        <x:v>刷怪怪物与权重</x:v>
+      </x:c>
+      <x:c r="H6" s="78"/>
+      <x:c r="I6" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J6" s="78" t="str">
+        <x:v>monsterId</x:v>
+      </x:c>
+      <x:c r="K6" s="78"/>
+      <x:c r="L6" s="78" t="str">
+        <x:v>int#ref=TbMonster</x:v>
+      </x:c>
+      <x:c r="M6" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N6" s="78" t="str">
+        <x:v>怪物ID</x:v>
+      </x:c>
+      <x:c r="O6" s="78"/>
+      <x:c r="P6" s="78"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="78"/>
+      <x:c r="B7" s="78"/>
+      <x:c r="C7" s="78"/>
+      <x:c r="D7" s="78"/>
+      <x:c r="E7" s="78"/>
+      <x:c r="F7" s="78"/>
+      <x:c r="G7" s="78"/>
+      <x:c r="H7" s="78"/>
+      <x:c r="I7" s="78"/>
+      <x:c r="J7" s="78" t="str">
+        <x:v>weight</x:v>
+      </x:c>
+      <x:c r="K7" s="78"/>
+      <x:c r="L7" s="78" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M7" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N7" s="78" t="str">
+        <x:v>正整数权重</x:v>
+      </x:c>
+      <x:c r="O7" s="78"/>
+      <x:c r="P7" s="78"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="78"/>
+      <x:c r="B8" s="78" t="str">
+        <x:v>RunAttributeModifier</x:v>
+      </x:c>
+      <x:c r="C8" s="78"/>
+      <x:c r="D8" s="79" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="78"/>
+      <x:c r="F8" s="78" t="str">
+        <x:v>:</x:v>
+      </x:c>
+      <x:c r="G8" s="78" t="str">
+        <x:v>局内属性修改项</x:v>
+      </x:c>
+      <x:c r="H8" s="78"/>
+      <x:c r="I8" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="J8" s="78" t="str">
+        <x:v>attributeId</x:v>
+      </x:c>
+      <x:c r="K8" s="78"/>
+      <x:c r="L8" s="78" t="str">
+        <x:v>int#ref=TbAttribute</x:v>
+      </x:c>
+      <x:c r="M8" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N8" s="78" t="str">
+        <x:v>属性ID</x:v>
+      </x:c>
+      <x:c r="O8" s="78"/>
+      <x:c r="P8" s="78"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="78"/>
+      <x:c r="B9" s="78"/>
+      <x:c r="C9" s="78"/>
+      <x:c r="D9" s="78"/>
+      <x:c r="E9" s="78"/>
+      <x:c r="F9" s="78"/>
+      <x:c r="G9" s="78"/>
+      <x:c r="H9" s="78"/>
+      <x:c r="I9" s="78"/>
+      <x:c r="J9" s="78" t="str">
+        <x:v>operation</x:v>
+      </x:c>
+      <x:c r="K9" s="78"/>
+      <x:c r="L9" s="78" t="str">
+        <x:v>EAttributeModifyOperation</x:v>
+      </x:c>
+      <x:c r="M9" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N9" s="78" t="str">
+        <x:v>修改操作</x:v>
+      </x:c>
+      <x:c r="O9" s="78"/>
+      <x:c r="P9" s="78"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="78"/>
+      <x:c r="B10" s="78"/>
+      <x:c r="C10" s="78"/>
+      <x:c r="D10" s="78"/>
+      <x:c r="E10" s="78"/>
+      <x:c r="F10" s="78"/>
+      <x:c r="G10" s="78"/>
+      <x:c r="H10" s="78"/>
+      <x:c r="I10" s="78"/>
+      <x:c r="J10" s="78" t="str">
+        <x:v>valueMilli</x:v>
+      </x:c>
+      <x:c r="K10" s="78"/>
+      <x:c r="L10" s="78" t="str">
+        <x:v>long</x:v>
+      </x:c>
+      <x:c r="M10" s="78" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="N10" s="78" t="str">
+        <x:v>Add为原单位乘1000；AddPercent为比例乘1000</x:v>
+      </x:c>
+      <x:c r="O10" s="78"/>
+      <x:c r="P10" s="78"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="J1:P1"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>